--- a/output/air/air_executive_report.xlsx
+++ b/output/air/air_executive_report.xlsx
@@ -228,7 +228,7 @@
       <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4095750" cy="1676400"/>
+    <ext cx="3876675" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -253,7 +253,7 @@
       <row>42</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4095750" cy="1714500"/>
+    <ext cx="3876675" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -278,7 +278,7 @@
       <row>42</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3457575" cy="2095500"/>
+    <ext cx="3876675" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -303,7 +303,7 @@
       <row>62</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3448050" cy="2095500"/>
+    <ext cx="3457575" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -428,7 +428,7 @@
       <row>102</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4095750" cy="1981200"/>
+    <ext cx="3457575" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -453,7 +453,7 @@
       <row>122</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3981450" cy="2095500"/>
+    <ext cx="4095750" cy="1676400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -478,7 +478,7 @@
       <row>122</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2266950" cy="2095500"/>
+    <ext cx="4095750" cy="1981200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -503,7 +503,7 @@
       <row>142</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3857625" cy="2085975"/>
+    <ext cx="3981450" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -528,7 +528,7 @@
       <row>142</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3829050" cy="2095500"/>
+    <ext cx="4095750" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -553,7 +553,7 @@
       <row>162</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3829050" cy="2095500"/>
+    <ext cx="2266950" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -578,7 +578,7 @@
       <row>162</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3829050" cy="2095500"/>
+    <ext cx="3867150" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -603,7 +603,7 @@
       <row>182</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3829050" cy="2095500"/>
+    <ext cx="3914775" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="19" name="Image 19" descr="Picture"/>
@@ -628,7 +628,7 @@
       <row>182</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3829050" cy="2095500"/>
+    <ext cx="3914775" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -653,7 +653,7 @@
       <row>202</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3829050" cy="2095500"/>
+    <ext cx="3914775" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
@@ -678,7 +678,7 @@
       <row>202</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4095750" cy="2000250"/>
+    <ext cx="3914775" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -703,7 +703,7 @@
       <row>222</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4095750" cy="2000250"/>
+    <ext cx="3914775" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -728,7 +728,7 @@
       <row>222</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4095750" cy="2000250"/>
+    <ext cx="3914775" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -736,6 +736,81 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>242</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4095750" cy="2000250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>242</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4095750" cy="2000250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>262</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4095750" cy="2000250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
